--- a/docs/PPG/Comitê de Ética em Pesquisa.xlsx
+++ b/docs/PPG/Comitê de Ética em Pesquisa.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB503B20-5512-2E42-BAF2-AED14F6F149B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E68FC81-61BA-0947-ACA1-B67EB32214FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="960" yWindow="680" windowWidth="24920" windowHeight="15540" activeTab="1" xr2:uid="{46CBE343-25B5-CE4C-8D60-80361989358C}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="62">
   <si>
     <t>Publicação</t>
   </si>
@@ -207,6 +207,12 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1nUMu-LSy-WYqPn7fdvX7tCz2v9_M3L86</t>
+  </si>
+  <si>
+    <t>2026-2</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1shBmXhiqpTrIiO7GE3ROoQIt-8fqApTx</t>
   </si>
 </sst>
 </file>
@@ -630,13 +636,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -704,7 +710,7 @@
     <hyperlink ref="C3" r:id="rId3" xr:uid="{BA79501F-7DFC-224C-9B55-7F76F4BEF84C}"/>
     <hyperlink ref="C6" r:id="rId4" xr:uid="{8103BA41-79FA-9443-9358-C552296EE622}"/>
     <hyperlink ref="C7" r:id="rId5" xr:uid="{19A55501-D948-714D-8DFC-CB2C726B94E4}"/>
-    <hyperlink ref="C2" r:id="rId6" xr:uid="{30569577-1462-DE42-ADB2-DC00BD8F68E6}"/>
+    <hyperlink ref="C2" r:id="rId6" xr:uid="{AA4DB890-F2A2-594C-A58E-EF4D661EEC09}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -712,7 +718,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1FC783F-BA40-3F4E-8A53-F6EED60F7198}">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.83203125" bestFit="1" customWidth="1"/>
@@ -733,112 +739,112 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>19</v>
       </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -846,21 +852,21 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -868,43 +874,43 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>2</v>
       </c>
-      <c r="B16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>2020</v>
-      </c>
-      <c r="B17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -912,81 +918,93 @@
         <v>2020</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
+        <v>2020</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20">
         <v>2014</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B20" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20">
+    <row r="21" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21">
         <v>2012</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B21" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>2008</v>
-      </c>
-      <c r="B21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22">
+        <v>2008</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23">
         <v>2005</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B23" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:C22">
-    <sortCondition descending="1" ref="A1:A22"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:C23">
+    <sortCondition descending="1" ref="A1:A23"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="C22" r:id="rId1" xr:uid="{88BB35E6-AD5D-7145-A3E0-1E04E9C7D1A6}"/>
-    <hyperlink ref="C17" r:id="rId2" xr:uid="{886EEA76-4AF4-6C42-B23D-AA71D928E812}"/>
-    <hyperlink ref="C18" r:id="rId3" xr:uid="{CAF9866D-81C8-EB42-8201-EF552BF654F5}"/>
-    <hyperlink ref="C16" r:id="rId4" xr:uid="{59179473-944E-4249-8238-E8F5D115804B}"/>
-    <hyperlink ref="C14" r:id="rId5" xr:uid="{79A34460-1B1D-6241-AE41-7D7B56AAC0E4}"/>
-    <hyperlink ref="C15" r:id="rId6" xr:uid="{1FC4FF28-157C-8B47-8F93-16F0B359AB79}"/>
-    <hyperlink ref="C20" r:id="rId7" xr:uid="{0561548C-AE21-694E-B21D-CFAE431D0896}"/>
-    <hyperlink ref="C19" r:id="rId8" xr:uid="{08D6F470-C6CE-4B42-AD3C-28C453701CEF}"/>
-    <hyperlink ref="C13" r:id="rId9" xr:uid="{7F61998E-85A7-3B4E-A136-A9D5B658B01E}"/>
-    <hyperlink ref="C10" r:id="rId10" xr:uid="{FCC8D137-421B-8C47-B665-295E040C7508}"/>
-    <hyperlink ref="C9" r:id="rId11" xr:uid="{C0E4DB13-5CF6-ED4B-AA92-B5AFF015CA9D}"/>
-    <hyperlink ref="C8" r:id="rId12" xr:uid="{5583E5C5-9926-AB49-A143-FEB09802801E}"/>
-    <hyperlink ref="C7" r:id="rId13" xr:uid="{382FF0DB-E3E6-FE49-9D70-006B7A4C3A86}"/>
-    <hyperlink ref="C11" r:id="rId14" xr:uid="{1A61FFF3-4EA0-A442-AD33-D66531F9DD8F}"/>
-    <hyperlink ref="C12" r:id="rId15" xr:uid="{909A5F5D-62EB-F543-867F-7D943C7E00A8}"/>
-    <hyperlink ref="C21" r:id="rId16" xr:uid="{F14215CB-AC62-5140-B5CF-0C11852A6703}"/>
-    <hyperlink ref="C5" r:id="rId17" xr:uid="{251BCF5F-BACA-B84E-A6EE-F4AE2FF2E699}"/>
-    <hyperlink ref="C4" r:id="rId18" xr:uid="{3D610B46-1C77-BC4D-AED5-F145629848E0}"/>
-    <hyperlink ref="C3" r:id="rId19" xr:uid="{BE86EA4F-BE04-964F-A9A9-06B77DA514B2}"/>
-    <hyperlink ref="C2" r:id="rId20" xr:uid="{5F6A901E-DFC1-1147-9104-427E9410CDC8}"/>
+    <hyperlink ref="C23" r:id="rId1" xr:uid="{88BB35E6-AD5D-7145-A3E0-1E04E9C7D1A6}"/>
+    <hyperlink ref="C18" r:id="rId2" xr:uid="{886EEA76-4AF4-6C42-B23D-AA71D928E812}"/>
+    <hyperlink ref="C19" r:id="rId3" xr:uid="{CAF9866D-81C8-EB42-8201-EF552BF654F5}"/>
+    <hyperlink ref="C17" r:id="rId4" xr:uid="{59179473-944E-4249-8238-E8F5D115804B}"/>
+    <hyperlink ref="C15" r:id="rId5" xr:uid="{79A34460-1B1D-6241-AE41-7D7B56AAC0E4}"/>
+    <hyperlink ref="C16" r:id="rId6" xr:uid="{1FC4FF28-157C-8B47-8F93-16F0B359AB79}"/>
+    <hyperlink ref="C21" r:id="rId7" xr:uid="{0561548C-AE21-694E-B21D-CFAE431D0896}"/>
+    <hyperlink ref="C20" r:id="rId8" xr:uid="{08D6F470-C6CE-4B42-AD3C-28C453701CEF}"/>
+    <hyperlink ref="C14" r:id="rId9" xr:uid="{7F61998E-85A7-3B4E-A136-A9D5B658B01E}"/>
+    <hyperlink ref="C11" r:id="rId10" xr:uid="{FCC8D137-421B-8C47-B665-295E040C7508}"/>
+    <hyperlink ref="C10" r:id="rId11" xr:uid="{C0E4DB13-5CF6-ED4B-AA92-B5AFF015CA9D}"/>
+    <hyperlink ref="C9" r:id="rId12" xr:uid="{5583E5C5-9926-AB49-A143-FEB09802801E}"/>
+    <hyperlink ref="C8" r:id="rId13" xr:uid="{382FF0DB-E3E6-FE49-9D70-006B7A4C3A86}"/>
+    <hyperlink ref="C12" r:id="rId14" xr:uid="{1A61FFF3-4EA0-A442-AD33-D66531F9DD8F}"/>
+    <hyperlink ref="C13" r:id="rId15" xr:uid="{909A5F5D-62EB-F543-867F-7D943C7E00A8}"/>
+    <hyperlink ref="C22" r:id="rId16" xr:uid="{F14215CB-AC62-5140-B5CF-0C11852A6703}"/>
+    <hyperlink ref="C6" r:id="rId17" xr:uid="{251BCF5F-BACA-B84E-A6EE-F4AE2FF2E699}"/>
+    <hyperlink ref="C5" r:id="rId18" xr:uid="{3D610B46-1C77-BC4D-AED5-F145629848E0}"/>
+    <hyperlink ref="C4" r:id="rId19" xr:uid="{BE86EA4F-BE04-964F-A9A9-06B77DA514B2}"/>
+    <hyperlink ref="C3" r:id="rId20" xr:uid="{5F6A901E-DFC1-1147-9104-427E9410CDC8}"/>
+    <hyperlink ref="C2" r:id="rId21" xr:uid="{09398E56-B2FC-AC4B-8912-73F033D29739}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
